--- a/Result/profitability/4419.xlsx
+++ b/Result/profitability/4419.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.27</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.3150000000000001</v>
+        <v>-0.3537500000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>23.105</v>
+        <v>23.39125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.51</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3800000000000001</v>
+        <v>-0.35</v>
       </c>
       <c r="N3" t="n">
-        <v>19.585</v>
+        <v>20.16125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.27</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3462500000000001</v>
+        <v>-0.3387500000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>16.835</v>
+        <v>16.72375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-3.55</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.745</v>
+        <v>-0.7525000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>3.672499999999999</v>
+        <v>3.399999999999999</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8412499999999999</v>
+        <v>-0.8225</v>
       </c>
       <c r="N6" t="n">
-        <v>-4.56625</v>
+        <v>-4.196250000000001</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.63</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.86375</v>
+        <v>-0.85125</v>
       </c>
       <c r="N7" t="n">
-        <v>-7.50625</v>
+        <v>-7.02</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>-0.45</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.87</v>
+        <v>-0.87375</v>
       </c>
       <c r="N8" t="n">
-        <v>-10.3775</v>
+        <v>-10.70625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>-0.85</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9424999999999999</v>
+        <v>-0.9425000000000001</v>
       </c>
       <c r="N9" t="n">
         <v>-15.045</v>
@@ -1899,7 +1899,7 @@
         <v>-0.06</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.87625</v>
+        <v>-0.8762500000000001</v>
       </c>
       <c r="N12" t="n">
         <v>-14.47125</v>
@@ -2026,7 +2026,7 @@
         <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.3075</v>
+        <v>-0.3075000000000001</v>
       </c>
       <c r="N13" t="n">
         <v>-4.891249999999999</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4419</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>702</v>
+      </c>
+      <c r="D75" t="n">
+        <v>512</v>
+      </c>
+      <c r="E75" t="n">
+        <v>190</v>
+      </c>
+      <c r="F75" t="n">
+        <v>27.07</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-50</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-7.10%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-54</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-51</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.31875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>26.06375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.02999999999999997</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.1111111111111109</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.629999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.08855218855218849</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-2.18</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.07452991452991453</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
